--- a/docs/sales/cases/2026-10-28-paint-factory-gr/named-workforce.xlsx
+++ b/docs/sales/cases/2026-10-28-paint-factory-gr/named-workforce.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="العمالة" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="مشتركون غير نشطين خارج البيان" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K32"/>
+  <dimension ref="A1:N32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -439,37 +440,52 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>الجنس</t>
+          <t>الميلاد</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>تاريخ الميلاد</t>
+          <t>العمر</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>العمر</t>
+          <t>الهوية (آخر 4)</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>الهوية (آخر 4)</t>
+          <t>حالة التأمينات</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>عدد الصفوف في الملف</t>
+          <t>الأجر الخاضع</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>ملاحظة الملف</t>
+          <t>الالتحاق</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
+          <t>أهلية 1445</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>ملاحظة البيان</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
           <t>مهنة بيع؟</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>صفوف مكررة</t>
         </is>
       </c>
     </row>
@@ -494,29 +510,42 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>ذكر</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
           <t>1992-11-27</t>
         </is>
       </c>
-      <c r="G2" t="n">
+      <c r="F2" t="n">
         <v>33</v>
       </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>••••5526</t>
+        </is>
+      </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>••••5526</t>
+          <t>نشط</t>
         </is>
       </c>
       <c r="I2" t="n">
+        <v>4000</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>2022-12-01</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="N2" t="n">
         <v>1</v>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>نعم</t>
-        </is>
       </c>
     </row>
     <row r="3">
@@ -540,29 +569,42 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>ذكر</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
           <t>1998-06-26</t>
         </is>
       </c>
-      <c r="G3" t="n">
+      <c r="F3" t="n">
         <v>28</v>
       </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>••••9761</t>
+        </is>
+      </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>••••9761</t>
+          <t>نشط</t>
         </is>
       </c>
       <c r="I3" t="n">
+        <v>4000</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>2023-05-10</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="N3" t="n">
         <v>1</v>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>نعم</t>
-        </is>
       </c>
     </row>
     <row r="4">
@@ -586,29 +628,29 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>ذكر</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
           <t>2005-07-19</t>
         </is>
       </c>
-      <c r="G4" t="n">
+      <c r="F4" t="n">
         <v>21</v>
       </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>••••6544</t>
+        </is>
+      </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>••••6544</t>
-        </is>
-      </c>
-      <c r="I4" t="n">
+          <t>غير نشط</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="N4" t="n">
         <v>1</v>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>لا</t>
-        </is>
       </c>
     </row>
     <row r="5">
@@ -632,29 +674,42 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>ذكر</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
           <t>1966-10-15</t>
         </is>
       </c>
-      <c r="G5" t="n">
+      <c r="F5" t="n">
         <v>60</v>
       </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>••••6329</t>
+        </is>
+      </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>••••6329</t>
+          <t>نشط</t>
         </is>
       </c>
       <c r="I5" t="n">
+        <v>4000</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>2024-11-26</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="N5" t="n">
         <v>1</v>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>لا</t>
-        </is>
       </c>
     </row>
     <row r="6">
@@ -678,29 +733,29 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>ذكر</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
           <t>2005-05-02</t>
         </is>
       </c>
-      <c r="G6" t="n">
+      <c r="F6" t="n">
         <v>21</v>
       </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>••••9419</t>
+        </is>
+      </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>••••9419</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
+          <t>غير نشط</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="N6" t="n">
         <v>1</v>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>لا</t>
-        </is>
       </c>
     </row>
     <row r="7">
@@ -722,23 +777,36 @@
           <t>بناء</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>ذكر</t>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>••••7187</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>••••7187</t>
+          <t>نشط</t>
         </is>
       </c>
       <c r="I7" t="n">
+        <v>3000</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>2022-12-12</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="N7" t="n">
         <v>3</v>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>لا</t>
-        </is>
       </c>
     </row>
     <row r="8">
@@ -760,23 +828,36 @@
           <t>سائق حافلة</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>ذكر</t>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>••••2081</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>••••2081</t>
+          <t>نشط</t>
         </is>
       </c>
       <c r="I8" t="n">
+        <v>3000</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="N8" t="n">
         <v>1</v>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>لا</t>
-        </is>
       </c>
     </row>
     <row r="9">
@@ -798,23 +879,36 @@
           <t>مندوب مشتريات</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>ذكر</t>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>••••5246</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>••••5246</t>
+          <t>نشط</t>
         </is>
       </c>
       <c r="I9" t="n">
+        <v>3000</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>2024-04-03</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="N9" t="n">
         <v>1</v>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>لا</t>
-        </is>
       </c>
     </row>
     <row r="10">
@@ -838,29 +932,42 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>ذكر</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
           <t>1993-04-03</t>
         </is>
       </c>
-      <c r="G10" t="n">
+      <c r="F10" t="n">
         <v>33</v>
       </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>••••7290</t>
+        </is>
+      </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>••••7290</t>
+          <t>نشط</t>
         </is>
       </c>
       <c r="I10" t="n">
+        <v>2000</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>2022-03-01</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="N10" t="n">
         <v>1</v>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>لا</t>
-        </is>
       </c>
     </row>
     <row r="11">
@@ -882,23 +989,36 @@
           <t>عامل تحميل وتنزيل</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>ذكر</t>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>••••0415</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>••••0415</t>
+          <t>نشط</t>
         </is>
       </c>
       <c r="I11" t="n">
+        <v>1350</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="N11" t="n">
         <v>1</v>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>لا</t>
-        </is>
       </c>
     </row>
     <row r="12">
@@ -920,23 +1040,36 @@
           <t>عامل تحميل وتنزيل</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>ذكر</t>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>••••9228</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>••••9228</t>
+          <t>نشط</t>
         </is>
       </c>
       <c r="I12" t="n">
+        <v>1600</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="N12" t="n">
         <v>1</v>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>لا</t>
-        </is>
       </c>
     </row>
     <row r="13">
@@ -958,23 +1091,36 @@
           <t>عامل تصنيع</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>ذكر</t>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>••••9097</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>••••9097</t>
+          <t>نشط</t>
         </is>
       </c>
       <c r="I13" t="n">
+        <v>1800</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>2023-04-01</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="N13" t="n">
         <v>1</v>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>لا</t>
-        </is>
       </c>
     </row>
     <row r="14">
@@ -996,23 +1142,36 @@
           <t>عامل تصنيع</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>ذكر</t>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>••••4099</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>••••4099</t>
+          <t>نشط</t>
         </is>
       </c>
       <c r="I14" t="n">
+        <v>1500</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>2022-12-14</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="N14" t="n">
         <v>1</v>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>لا</t>
-        </is>
       </c>
     </row>
     <row r="15">
@@ -1034,23 +1193,36 @@
           <t>عامل تصنيع</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>ذكر</t>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>••••5097</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>••••5097</t>
+          <t>نشط</t>
         </is>
       </c>
       <c r="I15" t="n">
+        <v>2000</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>2023-03-05</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="N15" t="n">
         <v>1</v>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>لا</t>
-        </is>
       </c>
     </row>
     <row r="16">
@@ -1072,23 +1244,36 @@
           <t>عامل تصنيع</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>ذكر</t>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>••••7000</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>••••7000</t>
+          <t>نشط</t>
         </is>
       </c>
       <c r="I16" t="n">
+        <v>1500</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>2024-04-03</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="N16" t="n">
         <v>1</v>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>لا</t>
-        </is>
       </c>
     </row>
     <row r="17">
@@ -1112,29 +1297,42 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>ذكر</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
           <t>1984-05-10</t>
         </is>
       </c>
-      <c r="G17" t="n">
+      <c r="F17" t="n">
         <v>42</v>
       </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>••••8342</t>
+        </is>
+      </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>••••8342</t>
+          <t>نشط</t>
         </is>
       </c>
       <c r="I17" t="n">
+        <v>1500</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>2022-12-11</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="N17" t="n">
         <v>1</v>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>لا</t>
-        </is>
       </c>
     </row>
     <row r="18">
@@ -1156,23 +1354,36 @@
           <t>عامل تنظيف مكاتب ومنشآت</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>ذكر</t>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>••••7562</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>••••7562</t>
+          <t>نشط</t>
         </is>
       </c>
       <c r="I18" t="n">
+        <v>1500</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="N18" t="n">
         <v>1</v>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>لا</t>
-        </is>
       </c>
     </row>
     <row r="19">
@@ -1194,23 +1405,36 @@
           <t>عامل تنظيف مكاتب ومنشآت</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>ذكر</t>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>••••1120</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>••••1120</t>
+          <t>نشط</t>
         </is>
       </c>
       <c r="I19" t="n">
+        <v>1350</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="N19" t="n">
         <v>1</v>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>لا</t>
-        </is>
       </c>
     </row>
     <row r="20">
@@ -1232,23 +1456,36 @@
           <t>عامل رافعات</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>ذكر</t>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>••••1420</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>••••1420</t>
+          <t>نشط</t>
         </is>
       </c>
       <c r="I20" t="n">
+        <v>2000</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>2023-05-07</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="N20" t="n">
         <v>1</v>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>لا</t>
-        </is>
       </c>
     </row>
     <row r="21">
@@ -1270,23 +1507,36 @@
           <t>محاسب</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>ذكر</t>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>••••2656</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>••••2656</t>
+          <t>نشط</t>
         </is>
       </c>
       <c r="I21" t="n">
+        <v>5000</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>2021-11-17</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="N21" t="n">
         <v>1</v>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>لا</t>
-        </is>
       </c>
     </row>
     <row r="22">
@@ -1308,23 +1558,36 @@
           <t>أخصائي مبيعات</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>ذكر</t>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>••••3314</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>••••3314</t>
+          <t>نشط</t>
         </is>
       </c>
       <c r="I22" t="n">
+        <v>3500</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="N22" t="n">
         <v>1</v>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>نعم</t>
-        </is>
       </c>
     </row>
     <row r="23">
@@ -1346,23 +1609,36 @@
           <t>جيولوجي</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>ذكر</t>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>••••3664</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>••••3664</t>
+          <t>نشط</t>
         </is>
       </c>
       <c r="I23" t="n">
+        <v>9000</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>2024-05-13</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="N23" t="n">
         <v>1</v>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>لا</t>
-        </is>
       </c>
     </row>
     <row r="24">
@@ -1386,29 +1662,42 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>ذكر</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
           <t>1983-03-10</t>
         </is>
       </c>
-      <c r="G24" t="n">
+      <c r="F24" t="n">
         <v>43</v>
       </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>••••4117</t>
+        </is>
+      </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>••••4117</t>
+          <t>نشط</t>
         </is>
       </c>
       <c r="I24" t="n">
+        <v>3000</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>2022-05-31</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="N24" t="n">
         <v>1</v>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>لا</t>
-        </is>
       </c>
     </row>
     <row r="25">
@@ -1430,28 +1719,41 @@
           <t>مندوب مبيعات</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>ذكر</t>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>••••0419</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>••••0419</t>
+          <t>نشط</t>
         </is>
       </c>
       <c r="I25" t="n">
+        <v>2718</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>بدون عقد</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="N25" t="n">
         <v>1</v>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>بدون عقد</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>نعم</t>
-        </is>
       </c>
     </row>
     <row r="26">
@@ -1473,28 +1775,41 @@
           <t>بائع مواد انشائية</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>ذكر</t>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>••••9865</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>••••9865</t>
+          <t>نشط</t>
         </is>
       </c>
       <c r="I26" t="n">
+        <v>2500</v>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>2021-11-17</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>رخصة العمل منتهية</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="N26" t="n">
         <v>1</v>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>رخصة العمل منتهية</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>نعم</t>
-        </is>
       </c>
     </row>
     <row r="27">
@@ -1516,23 +1831,36 @@
           <t>عامل تحميل وتنزيل</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>ذكر</t>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>••••2225</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>••••2225</t>
+          <t>نشط</t>
         </is>
       </c>
       <c r="I27" t="n">
+        <v>2551</v>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="N27" t="n">
         <v>1</v>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>لا</t>
-        </is>
       </c>
     </row>
     <row r="28">
@@ -1554,23 +1882,36 @@
           <t>عامل تعبئة وتغليف</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>ذكر</t>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>••••7314</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>••••7314</t>
+          <t>نشط</t>
         </is>
       </c>
       <c r="I28" t="n">
+        <v>4500</v>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>2023-04-14</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="N28" t="n">
         <v>1</v>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>لا</t>
-        </is>
       </c>
     </row>
     <row r="29">
@@ -1594,29 +1935,42 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>ذكر</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
           <t>1988-01-01</t>
         </is>
       </c>
-      <c r="G29" t="n">
+      <c r="F29" t="n">
         <v>38</v>
       </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>••••7393</t>
+        </is>
+      </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>••••7393</t>
+          <t>نشط</t>
         </is>
       </c>
       <c r="I29" t="n">
+        <v>8000</v>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>2021-11-17</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="N29" t="n">
         <v>2</v>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>لا</t>
-        </is>
       </c>
     </row>
     <row r="30">
@@ -1640,34 +1994,47 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>ذكر</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
           <t>1960-01-01</t>
         </is>
       </c>
-      <c r="G30" t="n">
+      <c r="F30" t="n">
         <v>66</v>
       </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>••••4856</t>
+        </is>
+      </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>••••4856</t>
+          <t>نشط</t>
         </is>
       </c>
       <c r="I30" t="n">
+        <v>2551</v>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>2024-01-01</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>رخصة العمل منتهية</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="N30" t="n">
         <v>1</v>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>رخصة العمل منتهية</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>لا</t>
-        </is>
       </c>
     </row>
     <row r="31">
@@ -1689,23 +2056,36 @@
           <t>مندوب مبيعات</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>ذكر</t>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>••••9472</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>••••9472</t>
+          <t>نشط</t>
         </is>
       </c>
       <c r="I31" t="n">
+        <v>3000</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>2022-01-19</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="N31" t="n">
         <v>1</v>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>نعم</t>
-        </is>
       </c>
     </row>
     <row r="32">
@@ -1729,28 +2109,1375 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>ذكر</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
           <t>1991-10-20</t>
         </is>
       </c>
-      <c r="G32" t="n">
+      <c r="F32" t="n">
         <v>35</v>
       </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>••••0869</t>
+        </is>
+      </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>••••0869</t>
+          <t>نشط</t>
         </is>
       </c>
       <c r="I32" t="n">
+        <v>6000</v>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="N32" t="n">
         <v>3</v>
       </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>لا</t>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D60"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>الاسم</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>الجنسية</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>الجنس</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>الهوية (آخر 4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>عمير حمدان عبيد الحازمي</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">السعودية </t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ذكر </t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>••••0154</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>فاطمه يسلم عوض ال حتيش</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">السعودية </t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">انثى </t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>••••2309</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>نوره علي صالح الصيعري</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">السعودية </t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">انثى </t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>••••9605</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>خالد علي محمد مسلبي</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">السعودية </t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ذكر </t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>••••9147</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>زهره يسلم عوض الصيعري</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">السعودية </t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">انثى </t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>••••9464</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>مريم حسين مرعي القحطاني</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">السعودية </t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">انثى </t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>••••4525</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>نوره ظافر سعيد القحطاني</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">السعودية </t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">انثى </t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>••••0534</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>نبيله يحي ابراهيم الفاهمي</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">السعودية </t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">انثى </t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>••••7865</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>فاطمه يسلم بن مبروك الصيعري</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">السعودية </t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">انثى </t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>••••3623</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>لؤلؤه مبارك مبروك الصيعري</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">السعودية </t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">انثى </t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>••••7348</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>محمد خليف عزير الفهيقي</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">السعودية </t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ذكر </t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>••••2310</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>سلطان مبارك مبروك الصيعري</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">السعودية </t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ذكر </t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>••••8349</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>صالح عبدالرحمن سالم العمر</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">السعودية </t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ذكر </t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>••••2684</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>سعود عبدالله بن علي الصيعري</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">السعودية </t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ذكر </t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>••••7751</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>ناله الحسن محمد المرضي</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">السعودية </t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">انثى </t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>••••2542</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>ريم خالد سعيد جرمه</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">السعودية </t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">انثى </t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>••••2744</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>نعمه مبروك عبيد الصيعري</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">السعودية </t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">انثى </t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>••••4225</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>بسام سعود بن عبدالعزيز الغانم</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">السعودية </t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ذكر </t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>••••6656</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>هادي منصور هادي الدوسري</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">السعودية </t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ذكر </t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>••••7391</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>ريان عبدالعزيز بن حمد العراجه</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">السعودية </t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ذكر </t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>••••3914</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>PLACEDO  VERGARA MARQUEZ</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">الفلبين </t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ذكر </t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>••••5157</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>فريدي   كاريلو</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">الفلبين </t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ذكر </t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>••••9910</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>حفيظ اسكندر  احمد</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>الهند</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ذكر </t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>••••1659</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>ABDULVAHAB ASAN MAIDEEN ROWTHER</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>الهند</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ذكر </t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>••••8069</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>منير باشا شي  شايك</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>الهند</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ذكر </t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>••••2343</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>محمد   أبوبكر</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>الهند</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ذكر </t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>••••3030</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>محمد   زهير اقبال</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>الهند</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ذكر </t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>••••3238</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>عباس   ابو بكر</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>الهند</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ذكر </t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>••••3501</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>سمير   محمد</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>الهند</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ذكر </t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>••••5399</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>بير محمد خان محمد اسماعيل</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>الهند</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ذكر </t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>••••5548</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>عزيز أنور  نورثن</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>الهند</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ذكر </t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>••••3140</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>احمد محمد موسي الدريبي</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>اليمن</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ذكر </t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>••••1111</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>صالح عمر - باراس</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>اليمن</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ذكر </t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>••••4035</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>اسماعيل محمد اسماعيل الهمداني</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>اليمن</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ذكر </t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>••••6087</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>علي احمد عمر الهيصمي</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>اليمن</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ذكر </t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>••••4752</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>علي عبدالله علي بارجاش</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>اليمن</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ذكر </t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>••••8262</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>علي يحيى ناصر المصعبي</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>اليمن</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ذكر </t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>••••2045</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>صالح علي سالم العبدلي</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>اليمن</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ذكر </t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>••••0245</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>علي عبدالله - بارجاش</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>اليمن</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ذكر </t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>••••9529</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>ناصر علي عبدالرب الصدام</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>اليمن</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ذكر </t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>••••3255</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>عادل موسى عبدالله الصباحي</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>اليمن</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ذكر </t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>••••9468</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>يحي ناصر عبدالله المزيدي</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>اليمن</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ذكر </t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>••••8451</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>علي طالب محمد بارجاش</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>اليمن</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ذكر </t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>••••2964</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>عبداللاه احمد صالح البكري</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>اليمن</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ذكر </t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>••••7522</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>معوض عمر محمد بارجاش</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>اليمن</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ذكر </t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>••••2631</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>محمد عبدالله احمد بارجاش</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>اليمن</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ذكر </t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>••••9459</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>جمال طالب عبدالله بارجاش</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>اليمن</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ذكر </t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>••••9962</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>باسل قاسم صالح مثنى</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>اليمن</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ذكر </t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>••••2658</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>صلاح علي احمد بن علي</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>اليمن</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ذكر </t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>••••0587</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>علي عبدالرحمن سالم العامري</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>اليمن</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ذكر </t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>••••3085</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>حسن علي احمد بارجاش</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>اليمن</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ذكر </t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>••••3764</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>جافيد خان  وارث قل</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">باكستان </t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ذكر </t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>••••2216</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>سيد زمان شير محمد</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">باكستان </t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ذكر </t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>••••2693</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>NOOR BAQI FAZAL MOHAMMAD</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">باكستان </t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ذكر </t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>••••8519</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>تاج الاسلام   عبدالجليل</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">بنغلادش </t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ذكر </t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>••••5193</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>MOHAMMAD DAUD  MIAH</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">بنغلادش </t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ذكر </t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>••••6827</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>NETTU   RAJBONGSHI</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">بنغلادش </t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ذكر </t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>••••8804</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>محمد فيصل حسين الكثيري</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>قبائل نازحة</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ذكر </t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>••••4842</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>بركة سعيد سالم المنهالي</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>قبائل نازحة</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">انثى </t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>••••9441</t>
         </is>
       </c>
     </row>
